--- a/results/full_birds_lgbm_summary/birds_PartialAbstention_summary.xlsx
+++ b/results/full_birds_lgbm_summary/birds_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.3203±0.0631</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.3173±0.0513</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.2902±0.0349</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.2846±0.0283</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9780±0.0027</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9393±0.0031</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8037±0.0102</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.6632±0.0131</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.6922±0.0420</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.3401±0.0522</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.1409±0.0307</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.0898±0.0204</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.6826±0.0734</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.4477±0.0535</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.3477±0.0468</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.3275±0.0556</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.6655±0.0562</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.3689±0.0514</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.1893±0.0337</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.1347±0.0284</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.9311±0.0097</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8349±0.0120</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.7095±0.0169</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6281±0.0122</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.6063±0.0559</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.3076±0.0454</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.1308±0.0276</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.0839±0.0188</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5503±0.0709</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.3636±0.0257</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.2058±0.0290</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1377±0.0250</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5598±0.0889</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.2878±0.0346</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1331±0.0221</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0837±0.0159</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.5932±0.0642</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.5707±0.0379</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.5647±0.0590</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.5477±0.0820</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.9500±0.1000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9438±0.0268</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.7464±0.1652</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7047±0.0527</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.7188±0.0427</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.4883±0.0515</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.2550±0.0410</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1599±0.0322</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.6901±0.0481</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.3699±0.0548</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.1564±0.0289</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.0920±0.0196</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7517±0.0488</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7288±0.0405</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.7039±0.0530</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6203±0.0786</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.7318±0.0451</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.3767±0.0144</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.0093±0.0114</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.4085±0.0684</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.1291±0.0319</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.0047±0.0063</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.3016±0.0628</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.2995±0.0418</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2630±0.0117</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.2815±0.0203</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9763±0.0027</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9350±0.0039</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.7871±0.0107</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.6217±0.0108</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6675±0.0366</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.3144±0.0508</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.1266±0.0212</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.0821±0.0167</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6919±0.0741</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.4640±0.0583</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.3660±0.0420</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.3468±0.0557</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.6571±0.0549</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.3594±0.0516</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.1800±0.0268</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.1278±0.0243</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.9261±0.0095</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8232±0.0132</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6841±0.0180</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.5814±0.0099</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5948±0.0547</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.2922±0.0438</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.1197±0.0196</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.0783±0.0159</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.5510±0.0661</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.3679±0.0258</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.2051±0.0248</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.1339±0.0231</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.5458±0.0676</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.2841±0.0315</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1303±0.0195</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0797±0.0145</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.6130±0.0658</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.6048±0.0363</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.6171±0.0414</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.6070±0.0985</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.9500±0.1000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.8652±0.1256</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.6931±0.1383</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.6541±0.0580</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.7088±0.0411</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.4822±0.0521</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.2484±0.0375</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1535±0.0291</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.6589±0.0446</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.3558±0.0532</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.1498±0.0260</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.0869±0.0174</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7687±0.0497</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7591±0.0361</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.7384±0.0406</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6664±0.0774</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.7225±0.0491</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.3550±0.0090</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.0047±0.0062</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.3887±0.0691</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.0987±0.0309</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.3259±0.0527</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.3283±0.0608</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.2841±0.0144</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.2802±0.0358</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9781±0.0028</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9395±0.0029</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8065±0.0101</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.6664±0.0128</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.6953±0.0432</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.3416±0.0541</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.1432±0.0304</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.0901±0.0212</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.6790±0.0681</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.4449±0.0531</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.3516±0.0423</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.3243±0.0596</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.6654±0.0551</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.3686±0.0521</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.1921±0.0329</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.1347±0.0296</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.9317±0.0094</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8353±0.0125</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.7132±0.0168</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6307±0.0117</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.6073±0.0562</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.3074±0.0459</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.1329±0.0270</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.0839±0.0196</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.5488±0.0625</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.3604±0.0249</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.2100±0.0282</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.1370±0.0261</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.5646±0.0871</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.2867±0.0345</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1361±0.0222</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0834±0.0168</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.5876±0.0555</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.5595±0.0507</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.5671±0.0293</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.5376±0.0820</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.9547±0.0905</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9479±0.0301</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.8091±0.0702</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.7111±0.0561</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.7194±0.0411</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.4884±0.0524</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2598±0.0403</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1594±0.0337</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.6946±0.0466</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.3711±0.0564</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.1596±0.0288</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.0919±0.0205</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.7474±0.0454</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7248±0.0362</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.7112±0.0428</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.6113±0.0825</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.7333±0.0469</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.3767±0.0144</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.0078±0.0085</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.4121±0.0730</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.1290±0.0341</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.0031±0.0038</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.3016±0.0628</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.3010±0.0433</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.2643±0.0146</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.2807±0.0180</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9763±0.0027</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9352±0.0035</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.7878±0.0099</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.6232±0.0126</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.6675±0.0366</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.3144±0.0511</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.1268±0.0207</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.0821±0.0177</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.6919±0.0741</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.4617±0.0576</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.3670±0.0407</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.3432±0.0594</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.6571±0.0549</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.3588±0.0516</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.1803±0.0262</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.1273±0.0258</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.9260±0.0095</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8232±0.0133</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.6844±0.0167</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.5821±0.0113</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5948±0.0547</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.2919±0.0438</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.1199±0.0190</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.0780±0.0168</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.5510±0.0661</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.3682±0.0270</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.2061±0.0245</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.1331±0.0238</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.5458±0.0676</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.2856±0.0336</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1310±0.0195</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0792±0.0150</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.6130±0.0658</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.6040±0.0344</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.6131±0.0327</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.6010±0.0991</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.9500±0.1000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.8652±0.1256</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.7541±0.0450</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.6444±0.0688</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.7088±0.0411</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.4826±0.0527</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.2501±0.0373</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1528±0.0306</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.6589±0.0446</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.3567±0.0542</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.1509±0.0258</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.0866±0.0183</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.7687±0.0497</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7570±0.0310</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.7436±0.0394</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.6590±0.0821</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.7225±0.0491</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.3550±0.0090</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.0047±0.0062</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.3887±0.0691</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.0987±0.0309</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.3650±0.0752</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.3640±0.0530</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.3263±0.0210</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.2831±0.0418</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9779±0.0025</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9380±0.0043</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.8128±0.0098</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.6879±0.0127</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.7072±0.0324</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.3436±0.0331</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.1498±0.0362</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.0972±0.0204</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.6598±0.0452</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.4299±0.0448</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.3251±0.0529</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.3242±0.0547</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.6622±0.0374</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.3613±0.0354</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.1921±0.0396</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.1422±0.0276</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.9320±0.0078</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8425±0.0099</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.7438±0.0117</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.6745±0.0134</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.6030±0.0397</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.2972±0.0294</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.1360±0.0328</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.0892±0.0186</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.5460±0.0731</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.3585±0.0351</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.2070±0.0320</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1440±0.0246</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.5849±0.0914</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.2920±0.0425</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1369±0.0245</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0886±0.0163</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.5519±0.0666</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.5532±0.0483</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.5217±0.0380</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.5444±0.0803</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.9333±0.1333</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9563±0.0218</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.8255±0.0388</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.6882±0.1297</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.7164±0.0398</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.4771±0.0476</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.2567±0.0438</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1675±0.0323</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.7176±0.0427</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.3722±0.0463</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.1612±0.0321</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.0979±0.0202</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.7161±0.0448</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.6704±0.0627</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.6429±0.0399</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.5919±0.0707</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.7349±0.0384</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.3705±0.0247</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.0155±0.0170</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.4075±0.0587</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.1154±0.0155</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.0094±0.0151</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.3379±0.0672</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.3235±0.0578</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.2789±0.0268</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.2757±0.0099</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9758±0.0021</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9313±0.0061</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.7813±0.0115</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.5996±0.0094</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.6733±0.0238</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.3056±0.0282</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.1265±0.0274</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.0832±0.0143</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.6760±0.0441</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.4397±0.0450</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.3535±0.0617</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.3772±0.0475</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.6504±0.0306</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.3417±0.0313</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.1766±0.0345</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.1311±0.0209</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.9254±0.0067</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.8255±0.0072</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.6994±0.0151</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.5799±0.0102</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.5842±0.0299</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.2707±0.0239</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.1188±0.0257</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.0795±0.0137</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.5460±0.0703</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.3536±0.0223</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.1998±0.0326</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.1379±0.0192</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.5561±0.0742</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.2772±0.0276</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1271±0.0237</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0814±0.0124</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.5801±0.0643</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.5926±0.0670</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.5848±0.0443</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.6483±0.0794</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.9333±0.1333</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9425±0.0235</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.7727±0.0420</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.6354±0.0608</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.7022±0.0367</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.4592±0.0382</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.2437±0.0435</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1557±0.0246</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.6713±0.0349</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.3446±0.0360</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.1480±0.0297</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.0878±0.0149</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.7371±0.0485</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.6936±0.0583</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7023±0.0503</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.6992±0.0486</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.7194±0.0345</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.3457±0.0223</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.0109±0.0116</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.3731±0.0394</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.0805±0.0095</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.0047±0.0094</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.3641±0.0726</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.3791±0.0578</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.3320±0.0281</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.2986±0.0397</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9778±0.0029</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9390±0.0041</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.8176±0.0106</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.6979±0.0128</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.7125±0.0313</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.3528±0.0375</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.1552±0.0397</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.0969±0.0199</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.6551±0.0456</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.4221±0.0457</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.3175±0.0553</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.3049±0.0432</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.6612±0.0353</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.3622±0.0380</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.1941±0.0416</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.1391±0.0254</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.9318±0.0072</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8447±0.0105</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.7492±0.0136</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.6841±0.0135</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5999±0.0396</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.2995±0.0338</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.1383±0.0348</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.0874±0.0173</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.5468±0.0662</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.3542±0.0344</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.2062±0.0313</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1392±0.0230</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.5878±0.0854</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.2925±0.0443</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1377±0.0243</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0864±0.0156</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.5492±0.0676</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.5365±0.0479</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.5009±0.0363</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.5048±0.0544</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.9333±0.1333</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9525±0.0278</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.8398±0.0423</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.7304±0.1011</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.7127±0.0352</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.4741±0.0490</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.2568±0.0459</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1637±0.0298</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.7208±0.0366</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.3743±0.0492</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.1625±0.0339</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.0963±0.0191</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.7062±0.0469</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.6533±0.0644</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.6250±0.0457</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.5559±0.0481</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.7302±0.0466</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.3783±0.0247</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.0155±0.0170</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.3965±0.0731</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.1263±0.0198</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.0094±0.0151</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.3338±0.0618</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.3226±0.0582</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.2764±0.0260</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.2710±0.0184</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9758±0.0019</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9316±0.0057</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.7815±0.0122</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.5983±0.0059</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.6754±0.0250</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.3062±0.0285</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.1260±0.0280</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.0817±0.0134</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.6781±0.0427</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.4397±0.0450</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.3487±0.0622</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.3697±0.0482</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.6524±0.0301</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.3421±0.0314</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.1754±0.0348</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.1287±0.0198</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.9254±0.0065</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.8254±0.0071</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.6979±0.0148</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.5769±0.0060</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5859±0.0289</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.2711±0.0240</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.1182±0.0265</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.0780±0.0129</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.5493±0.0658</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.3545±0.0229</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.1987±0.0332</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.1355±0.0178</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.5567±0.0737</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.2780±0.0279</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1266±0.0244</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0800±0.0115</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.5849±0.0608</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.5926±0.0670</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.5796±0.0432</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.6355±0.0869</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.9333±0.1333</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9387±0.0272</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.7705±0.0496</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.6405±0.0578</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.7022±0.0365</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.4603±0.0381</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.2418±0.0446</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1531±0.0228</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.6718±0.0360</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.3456±0.0367</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.1469±0.0304</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.0862±0.0138</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.7366±0.0482</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.6949±0.0577</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.6944±0.0522</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.6900±0.0492</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.7194±0.0315</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.3457±0.0223</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.0109±0.0116</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.3708±0.0337</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.0805±0.0095</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.0047±0.0094</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
